--- a/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0003T0006Z000C1N8_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0003T0006Z000C1N8_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>42.37004646700578</v>
+        <v>6.885132550888439</v>
       </c>
       <c r="D2" t="n">
-        <v>23.08920895673851</v>
+        <v>3.751996455470008</v>
       </c>
       <c r="E2" t="n">
-        <v>14.45322009422985</v>
+        <v>2.348648265312351</v>
       </c>
       <c r="F2" t="n">
-        <v>13.67858055972877</v>
+        <v>2.222769340955926</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>52.25430079941889</v>
+        <v>8.491323879905568</v>
       </c>
       <c r="D3" t="n">
-        <v>53.73704082577665</v>
+        <v>8.732269134188705</v>
       </c>
       <c r="E3" t="n">
-        <v>14.45322009422985</v>
+        <v>2.348648265312351</v>
       </c>
       <c r="F3" t="n">
-        <v>13.67858055972877</v>
+        <v>2.222769340955926</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>32.4354240093795</v>
+        <v>5.270756401524168</v>
       </c>
       <c r="D4" t="n">
-        <v>32.08328155893422</v>
+        <v>5.213533253326812</v>
       </c>
       <c r="E4" t="n">
-        <v>14.45322009422985</v>
+        <v>2.348648265312351</v>
       </c>
       <c r="F4" t="n">
-        <v>13.67858055972877</v>
+        <v>2.222769340955926</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>20.04231294596949</v>
+        <v>3.256875853720042</v>
       </c>
       <c r="D5" t="n">
-        <v>21.6481376450832</v>
+        <v>3.51782236732602</v>
       </c>
       <c r="E5" t="n">
-        <v>14.45322009422985</v>
+        <v>2.348648265312351</v>
       </c>
       <c r="F5" t="n">
-        <v>13.67858055972877</v>
+        <v>2.222769340955926</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>39.78745850829957</v>
+        <v>6.46546200759868</v>
       </c>
       <c r="D6" t="n">
-        <v>34.51448971084464</v>
+        <v>5.608604578012254</v>
       </c>
       <c r="E6" t="n">
-        <v>14.45322009422985</v>
+        <v>2.348648265312351</v>
       </c>
       <c r="F6" t="n">
-        <v>13.67858055972877</v>
+        <v>2.222769340955926</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>8.888163447185338</v>
+        <v>1.444326560167617</v>
       </c>
       <c r="D7" t="n">
-        <v>9.45917841134705</v>
+        <v>1.537116491843896</v>
       </c>
       <c r="E7" t="n">
-        <v>14.45322009422985</v>
+        <v>2.348648265312351</v>
       </c>
       <c r="F7" t="n">
-        <v>13.67858055972877</v>
+        <v>2.222769340955926</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
